--- a/documentation/scrum/Sprint_1_Burndown.xlsx
+++ b/documentation/scrum/Sprint_1_Burndown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://micloud365-my.sharepoint.com/personal/imashai_millenniumitesp_com/Documents/Desktop/MSc BInA/Academics/3-Interactive Visualization/Assesment/Project/group4-interactive-visualisation/documentation/scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_2C750128247682E81B996B25C37309B4575122DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{781C5399-FA53-4FAD-A50D-057EC92D9CE9}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="11_2C750128247682E81B996B25C37309B4575122DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F62A7CD0-3559-4AED-81D6-261419FF3214}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>Day</t>
   </si>
@@ -61,18 +61,12 @@
     <t>Day 0</t>
   </si>
   <si>
-    <t>[Start Date]</t>
-  </si>
-  <si>
     <t>Sprint starts; 20 checklist items planned.</t>
   </si>
   <si>
     <t>Day 1</t>
   </si>
   <si>
-    <t>[Date]</t>
-  </si>
-  <si>
     <t>Enter actual remaining items from Trello.</t>
   </si>
   <si>
@@ -88,9 +82,6 @@
     <t>Day 5</t>
   </si>
   <si>
-    <t>[End Date]</t>
-  </si>
-  <si>
     <t>Sprint end; enter actual remaining items from Trello.</t>
   </si>
   <si>
@@ -302,13 +293,34 @@
   </si>
   <si>
     <t>Keep dated Trello screenshots or board history if your lecturer requires progress evidence.</t>
+  </si>
+  <si>
+    <t>Day 6</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Samarakoon</t>
+  </si>
+  <si>
+    <t>Ilamperuma</t>
+  </si>
+  <si>
+    <t>De Silva</t>
+  </si>
+  <si>
+    <t>Allocated</t>
+  </si>
+  <si>
+    <t>Day Number</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,6 +332,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -347,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -356,6 +374,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -428,9 +449,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Sprint 1 Burndown'!$A$2:$A$7</c:f>
+              <c:f>'Sprint 1 Burndown'!$A$2:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Day 0</c:v>
                 </c:pt>
@@ -448,32 +469,38 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>Day 5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Day 6</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint 1 Burndown'!$C$2:$C$7</c:f>
+              <c:f>'Sprint 1 Burndown'!$C$2:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -510,9 +537,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>'Sprint 1 Burndown'!$A$2:$A$7</c:f>
+              <c:f>'Sprint 1 Burndown'!$A$2:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Day 0</c:v>
                 </c:pt>
@@ -530,16 +557,40 @@
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>Day 5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Day 6</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint 1 Burndown'!$D$2:$D$7</c:f>
+              <c:f>'Sprint 1 Burndown'!$D$2:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -683,6 +734,10 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -970,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1005,127 +1060,160 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
+      <c r="B2" s="4">
+        <v>46285</v>
       </c>
       <c r="C2" s="2">
         <v>20</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>15</v>
+      </c>
       <c r="E2" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4">
+        <v>46286</v>
+      </c>
+      <c r="C3" s="2">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="str">
-        <f t="shared" ref="E3:E8" si="0">IF(OR(D3="",D2=""),"",D2-D3)</f>
-        <v/>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4">
+        <v>46287</v>
+      </c>
+      <c r="C4" s="2">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" ref="E3:E9" si="0">IF(OR(D4="",D3=""),"",D3-D4)</f>
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4">
+        <v>46288</v>
+      </c>
+      <c r="C5" s="2">
+        <v>10</v>
+      </c>
+      <c r="D5" s="2">
+        <v>7</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="str">
+      <c r="B6" s="4">
+        <v>46289</v>
+      </c>
+      <c r="C6" s="2">
+        <v>7</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="4">
+        <v>46290</v>
+      </c>
+      <c r="C7" s="2">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="4">
+        <v>46291</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="2">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F8" s="2"/>
+      <c r="F9" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1133,7 +1221,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1142,426 +1230,553 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B2" t="s">
         <v>22</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
         <v>28</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>32</v>
       </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D5" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>34</v>
       </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>38</v>
       </c>
-      <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>40</v>
       </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>41</v>
       </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>42</v>
       </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="B10" t="s">
         <v>43</v>
       </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>44</v>
       </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>45</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
         <v>46</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>47</v>
       </c>
-      <c r="D10" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="B12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" t="s">
         <v>48</v>
       </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
         <v>49</v>
       </c>
-      <c r="D11" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="B13" t="s">
         <v>50</v>
       </c>
-      <c r="B12" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>51</v>
       </c>
-      <c r="D12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>52</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
         <v>53</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>54</v>
       </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
         <v>55</v>
       </c>
-      <c r="B14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>56</v>
       </c>
-      <c r="D14" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
         <v>57</v>
       </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>58</v>
       </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
         <v>59</v>
       </c>
-      <c r="B16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
         <v>60</v>
       </c>
-      <c r="D16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
+      <c r="B18" t="s">
         <v>61</v>
       </c>
-      <c r="B17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>62</v>
       </c>
-      <c r="D17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>63</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" t="s">
         <v>64</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>65</v>
       </c>
-      <c r="D18" t="s">
-        <v>27</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
+      <c r="B20" t="s">
         <v>66</v>
       </c>
-      <c r="B19" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
         <v>68</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" t="s">
         <v>69</v>
       </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
-      <c r="F20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>71</v>
-      </c>
-      <c r="B21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" t="s">
-        <v>72</v>
-      </c>
       <c r="D21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+      <c r="G21" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1581,34 +1796,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1616,31 +1831,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
